--- a/en/downloads/data-excel/6.2.1.1.xlsx
+++ b/en/downloads/data-excel/6.2.1.1.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55FEDF9-A5E5-45A1-9C5C-B291D8E562BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13920" windowHeight="8145"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="таб.8.19" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">таб.8.19!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'таб.8.19'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
@@ -147,7 +148,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -315,7 +316,7 @@
     <xf numFmtId="38" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="40" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -331,10 +332,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -343,36 +344,29 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -387,17 +381,17 @@
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="3"/>
-    <cellStyle name="Обычный 2 2" xfId="4"/>
-    <cellStyle name="Обычный 3" xfId="5"/>
-    <cellStyle name="Обычный 4" xfId="6"/>
-    <cellStyle name="Обычный 5" xfId="2"/>
-    <cellStyle name="Обычный_80102" xfId="1"/>
-    <cellStyle name="полужирный" xfId="7"/>
-    <cellStyle name="Процентный 2" xfId="8"/>
-    <cellStyle name="Процентный 3" xfId="9"/>
-    <cellStyle name="Тысячи [0]_Dannee" xfId="10"/>
-    <cellStyle name="Тысячи_Dannee" xfId="11"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный_80102" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="полужирный" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Процентный 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Процентный 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Тысячи [0]_Dannee" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Тысячи_Dannee" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -413,9 +407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -453,9 +447,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -490,7 +484,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -525,7 +519,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -698,18 +692,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="37.140625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="39.75" customHeight="1">
+    <row r="1" spans="1:17" ht="39.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
@@ -719,47 +713,43 @@
       <c r="C1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.75" customHeight="1">
-      <c r="A2" s="30" t="s">
+    </row>
+    <row r="2" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A2" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-    </row>
-    <row r="3" spans="1:16" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-    </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1">
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+    </row>
+    <row r="3" spans="1:17" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+    </row>
+    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -769,47 +759,50 @@
       <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="26">
         <v>2011</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="26">
         <v>2012</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="26">
         <v>2013</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="26">
         <v>2014</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="26">
         <v>2015</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="26">
         <v>2016</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="26">
         <v>2017</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="26">
         <v>2018</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="26">
         <v>2019</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="26">
         <v>2020</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="26">
         <v>2021</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="26">
         <v>2022</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="26">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1">
+      <c r="Q4" s="26">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -819,47 +812,50 @@
       <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>25.409176121708509</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="20">
         <v>26.881444427092088</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="20">
         <v>28.022386195061991</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="20">
         <v>28.074761567940566</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="20">
         <v>28.6</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="20">
         <v>30.191440257916568</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="20">
         <v>31.303387202705807</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K5" s="20">
         <v>31.5</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="20">
         <v>31.5</v>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="20">
         <v>34.377950588852634</v>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="27">
         <v>40.007977647471066</v>
       </c>
-      <c r="O5" s="32">
+      <c r="O5" s="27">
         <v>42.620582506455563</v>
       </c>
-      <c r="P5" s="32">
+      <c r="P5" s="27">
         <v>48.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1">
+      <c r="Q5" s="20">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>13</v>
       </c>
@@ -869,47 +865,50 @@
       <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="21">
         <v>2.9698183576213828</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="21">
         <v>3.6528907207307562</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="21">
         <v>4.7830634792651834</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="21">
         <v>5.2203799951019692</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="21">
         <v>6.7</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="21">
         <v>6.3050836536583503</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="21">
         <v>12.02195723459222</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="21">
         <v>9.1</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="21">
         <v>5.9</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="21">
         <v>4.8358243107925931</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="28">
         <v>5.7072514621689896</v>
       </c>
-      <c r="O6" s="33">
+      <c r="O6" s="28">
         <v>8.1443914479075037</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="28">
         <v>8.6767564891727478</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1">
+      <c r="Q6" s="21">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
@@ -919,47 +918,50 @@
       <c r="C7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="21">
         <v>8.771071126047806</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="21">
         <v>11.685930422822452</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="21">
         <v>5.4949637548237895</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="21">
         <v>5.6093293109930702</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="21">
         <v>5.6</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="21">
         <v>8.3444422578354285</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="21">
         <v>14.376772854149495</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="21">
         <v>9</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="21">
         <v>6.2</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="21">
         <v>5.9543034993102522</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="28">
         <v>8.9893229854028949</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="28">
         <v>10.715961386284755</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="28">
         <v>12.226605469730881</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1">
+      <c r="Q7" s="21">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
@@ -969,47 +971,50 @@
       <c r="C8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="21">
         <v>15.385834469858461</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="21">
         <v>18.787621589627332</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="21">
         <v>25.086019797787305</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="21">
         <v>24.16337389503758</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="21">
         <v>27.1</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="21">
         <v>29.986451460885956</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="21">
         <v>38.652292109660173</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="21">
         <v>41.4</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="21">
         <v>30.5</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="21">
         <v>51.21106605430419</v>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="28">
         <v>66.307512472824584</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="28">
         <v>81.977461999426666</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="28">
         <v>78.520866131691164</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1">
+      <c r="Q8" s="21">
+        <v>89.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
@@ -1019,47 +1024,50 @@
       <c r="C9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="21">
         <v>5.5505440710783667</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="21">
         <v>6.2654040242010662</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="21">
         <v>12.479391864169072</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="21">
         <v>14.196021800562242</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="21">
         <v>13.7</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="21">
         <v>16.983672902290355</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="21">
         <v>17.842313387212478</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="21">
         <v>20.399999999999999</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="21">
         <v>21.8</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="21">
         <v>27.156801192263725</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="28">
         <v>23.475213049310256</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="28">
         <v>29.828871240443185</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="28">
         <v>59.466452648968115</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1">
+      <c r="Q9" s="21">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>32</v>
       </c>
@@ -1069,47 +1077,50 @@
       <c r="C10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="21">
         <v>8.251864137737444</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="21">
         <v>7.8249612780867457</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="21">
         <v>0.18990600164335175</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="21">
         <v>0.72699386003617872</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="21">
         <v>0.5</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="21">
         <v>0.44988170209128941</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="21">
         <v>7.1535875241433584E-3</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="21">
         <v>0.5</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="21">
         <v>1.7</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="21">
         <v>0.94331159862228353</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="28">
         <v>9.8045372040896162</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10" s="28">
         <v>9.7218425128664112</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="28">
         <v>26.635270208942913</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1">
+      <c r="Q10" s="21">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>21</v>
       </c>
@@ -1119,47 +1130,50 @@
       <c r="C11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="21">
         <v>9.0342374653142219</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="21">
         <v>7.8405792790457536</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="21">
         <v>5.098828421834944</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="21">
         <v>5.4933320389763258</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="21">
         <v>6.5</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="21">
         <v>6.5165588869292579</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="21">
         <v>6.137177145637291</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="21">
         <v>6</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L11" s="21">
         <v>6.2</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="21">
         <v>7.8509592890793316</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="28">
         <v>9.3737779268960448</v>
       </c>
-      <c r="O11" s="33">
+      <c r="O11" s="28">
         <v>8.6167819403064012</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="28">
         <v>8.166450559693871</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1">
+      <c r="Q11" s="21">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>23</v>
       </c>
@@ -1169,48 +1183,51 @@
       <c r="C12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="21">
         <v>41.925111326422567</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="21">
         <v>46.114485989829575</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="21">
         <v>46.19385190513168</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="21">
         <v>49.202745383444821</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="21">
         <v>48.7</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="21">
         <v>50.971427171906761</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="21">
         <v>48.935048468284563</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="21">
         <v>56.8</v>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="21">
         <v>63.3</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="21">
         <v>64.733302669743793</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="28">
         <v>70.457032471318783</v>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="28">
         <v>69.915337594090886</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="28">
         <v>74.601894583630667</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="Q12" s="21">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1">
+      <c r="A13" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="12" t="s">
@@ -1219,119 +1236,125 @@
       <c r="C13" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="21">
         <v>84.554249579977053</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="21">
         <v>85.140508968304715</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="21">
         <v>98.608136326848182</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="21">
         <v>99.390116337241565</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="21">
         <v>98.6</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="21">
         <v>99.663698159511753</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="21">
         <v>97.392326489136082</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="21">
         <v>96.5</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="21">
         <v>96.1</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="21">
         <v>97.67954817102779</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="28">
         <v>98.411252120183207</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="28">
         <v>99.08571752721997</v>
       </c>
-      <c r="P13" s="33">
+      <c r="P13" s="28">
         <v>99.168063426054971</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="17" t="s">
+      <c r="Q13" s="21">
+        <v>99.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" thickBot="1">
+      <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="22">
         <v>28.731700012670331</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="22">
         <v>27.932014266053006</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="22">
         <v>28.2</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="22">
         <v>29.548534012471357</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="22">
         <v>25.391510887517011</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="22">
         <v>25.5</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="22">
         <v>30.9</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="22">
         <v>46.725153243037099</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="29">
         <v>63.900563564170795</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="29">
         <v>64.805252627098838</v>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="29">
         <v>70.956108992253434</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
+      <c r="Q14" s="22">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="13.5" customHeight="1">
+      <c r="A15" s="23"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="19" spans="12:12" ht="12.75" customHeight="1"/>
-    <row r="22" spans="12:12" s="15" customFormat="1" ht="15">
-      <c r="L22" s="16"/>
+    <row r="22" spans="12:12" s="14" customFormat="1" ht="15">
+      <c r="L22" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
